--- a/artfynd/A 45031-2023 artfynd.xlsx
+++ b/artfynd/A 45031-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 45031-2023 artfynd.xlsx
+++ b/artfynd/A 45031-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>110047865</v>
+        <v>110047869</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>602338.8722575287</v>
+        <v>602349</v>
       </c>
       <c r="R2" t="n">
-        <v>7306876.457795986</v>
+        <v>7306874</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2022-08-24</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-08-24</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>110047869</v>
+        <v>110047865</v>
       </c>
       <c r="B3" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>602348.8204905066</v>
+        <v>602339</v>
       </c>
       <c r="R3" t="n">
-        <v>7306873.535923985</v>
+        <v>7306876</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,19 +840,9 @@
           <t>2022-08-24</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-08-24</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,118 +866,6 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>110047823</v>
-      </c>
-      <c r="B4" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Nya Bergnäs, Pi lm</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>602351.4830671153</v>
-      </c>
-      <c r="R4" t="n">
-        <v>7306890.838289149</v>
-      </c>
-      <c r="S4" t="n">
-        <v>10</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Pite lappmark</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2022-08-24</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2022-08-24</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>Robert Sandberg</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>Jonas Nordenström</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 45031-2023 artfynd.xlsx
+++ b/artfynd/A 45031-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,45 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>110047869</v>
+        <v>134763634</v>
       </c>
       <c r="B2" t="n">
-        <v>83173</v>
+        <v>92201</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>67</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Nya Bergnäs, Pi lm</t>
+          <t>Naturskog vid Abborrsjön, NÖ om Bergnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>602349</v>
+        <v>602280</v>
       </c>
       <c r="R2" t="n">
-        <v>7306874</v>
+        <v>7306904</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-08-24</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-08-24</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -756,26 +756,31 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Luckig och lövrik, urskogsartad granskog</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Robert Sandberg</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jonas Nordenström</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>110047865</v>
+        <v>134763623</v>
       </c>
       <c r="B3" t="n">
-        <v>79327</v>
+        <v>78393</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,34 +788,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Nya Bergnäs, Pi lm</t>
+          <t>Naturskog vid Abborrsjön, NÖ om Bergnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>602339</v>
+        <v>602335</v>
       </c>
       <c r="R3" t="n">
-        <v>7306876</v>
+        <v>7306912</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -837,12 +842,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-08-24</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-08-24</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -853,19 +858,1442 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Luckig och lövrik, urskogsartad granskog</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>134763624</v>
+      </c>
+      <c r="B4" t="n">
+        <v>78393</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>314</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vitskaftad svartspik</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis viridialba</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Kremp.) A.F.W.Schmidt</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Naturskog vid Abborrsjön, NÖ om Bergnäs, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>602067</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7306957</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Luckig och lövrik, urskogsartad granskog</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>134763626</v>
+      </c>
+      <c r="B5" t="n">
+        <v>92245</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>658</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Naturskog vid Abborrsjön, NÖ om Bergnäs, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>602282</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7306909</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Luckig och lövrik, urskogsartad granskog</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>134763629</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91974</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Naturskog vid Abborrsjön, NÖ om Bergnäs, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>602228</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7306889</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Luckig och lövrik, urskogsartad granskog</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>134763631</v>
+      </c>
+      <c r="B7" t="n">
+        <v>91974</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Naturskog vid Abborrsjön, NÖ om Bergnäs, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>602286</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7306903</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Luckig och lövrik, urskogsartad granskog</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>134763635</v>
+      </c>
+      <c r="B8" t="n">
+        <v>91988</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Naturskog vid Abborrsjön, NÖ om Bergnäs, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>602055</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7306999</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Luckig och lövrik, urskogsartad granskog</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>134763636</v>
+      </c>
+      <c r="B9" t="n">
+        <v>91988</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Naturskog vid Abborrsjön, NÖ om Bergnäs, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>602422</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7306857</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Luckig och lövrik, urskogsartad granskog</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>110047869</v>
+      </c>
+      <c r="B10" t="n">
+        <v>83173</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Nya Bergnäs, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>602349</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7306874</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2022-08-24</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2022-08-24</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
           <t>Robert Sandberg</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX10" t="inlineStr">
         <is>
           <t>Jonas Nordenström</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>110047865</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Nya Bergnäs, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>602339</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7306876</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2022-08-24</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2022-08-24</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Robert Sandberg</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>134763625</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Naturskog vid Abborrsjön, NÖ om Bergnäs, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>602429</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7306845</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Luckig och lövrik, urskogsartad granskog</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>134763630</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Naturskog vid Abborrsjön, NÖ om Bergnäs, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>602305</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7306902</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Luckig och lövrik, urskogsartad granskog</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>134763632</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Naturskog vid Abborrsjön, NÖ om Bergnäs, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>602369</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7306857</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Luckig och lövrik, urskogsartad granskog</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>134763638</v>
+      </c>
+      <c r="B15" t="n">
+        <v>83358</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Naturskog vid Abborrsjön, NÖ om Bergnäs, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>602336</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7306910</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Luckig och lövrik, urskogsartad granskog</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>134763627</v>
+      </c>
+      <c r="B16" t="n">
+        <v>106309</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Naturskog vid Abborrsjön, NÖ om Bergnäs, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>602063</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7306946</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Örtrikt bäckdråg i urskogsartad granskog</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>134763637</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Naturskog vid Abborrsjön, NÖ om Bergnäs, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>602062</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7306953</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Örtrikt bäckdråg i urskogsartad granskog</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 45031-2023 artfynd.xlsx
+++ b/artfynd/A 45031-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134763634</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134763623</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134763624</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134763626</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134763629</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1284,6 +1314,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134763631</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1386,6 +1421,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134763635</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1488,6 +1528,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134763636</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1585,6 +1630,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110047869</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1682,6 +1732,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110047865</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1784,6 +1839,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134763630</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1886,6 +1946,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134763632</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1988,6 +2053,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134763638</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2090,6 +2160,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134763627</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2192,6 +2267,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134763637</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2294,8 +2374,31 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134763625</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>